--- a/spec/fixtures/ssp_sample.xlsx
+++ b/spec/fixtures/ssp_sample.xlsx
@@ -330,21 +330,21 @@
   <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="19.8" min="1" max="1" bestFit="1" customWidth="1"/>
+    <col width="14.3" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="42.900000000000006" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="91.30000000000001" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="80.30000000000001" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="77.0" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="41.800000000000004" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="15.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="15.400000000000002" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="12.100000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="26.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="19.8" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="20.900000000000002" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="19.8" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="22.0" min="12" max="12" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="22.0" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="15.400000000000002" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
     <col width="34.1" min="16" max="16" bestFit="1" customWidth="1"/>
     <col width="39.6" min="17" max="17" bestFit="1" customWidth="1"/>
   </cols>
@@ -352,87 +352,87 @@
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t>Paragraph/ReqID</t>
+          <t>control-id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>control-title</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
-          <t>Stated Requirement</t>
+          <t>control-statement</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>Private Implementation</t>
+          <t>implementation-statement</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
-          <t>Public Implementation</t>
+          <t>implementation-summary</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>remarks</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>implementation-status</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
-          <t>Expected Completion</t>
+          <t>completion-date</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>control-class</t>
         </is>
       </c>
       <c r="J1" s="0" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>control-priority</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
         <is>
-          <t>Responsible Entities</t>
+          <t>responsible-roles</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
         <is>
-          <t>Control Owner</t>
+          <t>responsible-party</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
-          <t>Type/Use As</t>
+          <t>control-application</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
         <is>
-          <t>Inherited From</t>
+          <t>inherited-from</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
         <is>
-          <t>Provided As</t>
+          <t>coverage-level</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
         <is>
-          <t>Control Origination</t>
+          <t>control-type</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>change-history</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,11 @@
           <t>System Specific</t>
         </is>
       </c>
-      <c r="N2" s="0"/>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="O2" s="0" t="inlineStr">
         <is>
           <t>Implemented</t>
@@ -520,30 +524,66 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0"/>
-      <c r="B3" s="0"/>
-      <c r="C3" s="0"/>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Provider statement: IAM system enforces MFA for all privileged users.</t>
         </is>
       </c>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Implemented</t>
         </is>
       </c>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0"/>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
           <t>IAM Team</t>
         </is>
       </c>
-      <c r="L3" s="0"/>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
           <t>Provider</t>
@@ -564,7 +604,11 @@
           <t>Inherited from provider</t>
         </is>
       </c>
-      <c r="Q3" s="0"/>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -632,7 +676,11 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="N4" s="0"/>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="O4" s="0" t="inlineStr">
         <is>
           <t>Configured</t>
@@ -675,13 +723,21 @@
           <t>Access enforcement mechanisms are tested during annual assessments.</t>
         </is>
       </c>
-      <c r="F5" s="0"/>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Implemented</t>
         </is>
       </c>
-      <c r="H5" s="0"/>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
           <t>Technical</t>
@@ -707,7 +763,11 @@
           <t>System Specific</t>
         </is>
       </c>
-      <c r="N5" s="0"/>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="O5" s="0" t="inlineStr">
         <is>
           <t>Implemented</t>
@@ -718,7 +778,11 @@
           <t>System Specific</t>
         </is>
       </c>
-      <c r="Q5" s="0"/>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
